--- a/src/lab3/v3/results/charts.xlsx
+++ b/src/lab3/v3/results/charts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu\data\www_me\vu_java\parallel\src\lab3\v3\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DAF05FD-0604-45ED-BEF6-D6B5BA2430FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52E072F6-55DC-43E0-8566-FBB251317279}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25275" yWindow="3285" windowWidth="26460" windowHeight="15435" xr2:uid="{3B0F670E-E01A-4267-849E-8CF26EF91A70}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21240" xr2:uid="{3B0F670E-E01A-4267-849E-8CF26EF91A70}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,45 +36,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
   <si>
     <t xml:space="preserve"> Masyvo dydis      </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 2^14 (16384)      </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 2^15 (32768)      </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 2^16 (65536)      </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 2^17 (131072)     </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 2^18 (262144)     </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 2^19 (524288)     </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 2^20 (1048576)    </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 2^21 (2097152)    </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 2^22 (4194304)    </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 2^23 (8388608)    </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 2^24 (16777216)   </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 2^25 (33554432)   </t>
   </si>
   <si>
     <t>1 gija</t>
@@ -108,6 +72,48 @@
   </si>
   <si>
     <t>Pokytis nuo 1 gijos (%)</t>
+  </si>
+  <si>
+    <t>idealus</t>
+  </si>
+  <si>
+    <t>2^25 idealus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2^14 (16384)      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2^15 (32768)      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2^16 (65536)      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2^17 (131072)     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2^18 (262144)     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2^19 (524288)     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2^20 (1048576)    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2^21 (2097152)    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2^22 (4194304)    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2^23 (8388608)    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2^24 (16777216)   </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2^25 (33554432)   </t>
   </si>
 </sst>
 </file>
@@ -154,7 +160,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -243,18 +249,28 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
@@ -268,9 +284,15 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -307,7 +329,7 @@
     <c:plotArea>
       <c:layout/>
       <c:lineChart>
-        <c:grouping val="stacked"/>
+        <c:grouping val="standard"/>
         <c:varyColors val="0"/>
         <c:ser>
           <c:idx val="0"/>
@@ -318,7 +340,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v> 2^14 (16384)      </c:v>
+                  <c:v>2^14 (16384)      </c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -365,7 +387,6 @@
                 <a:endParaRPr lang="lt-LT"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="t"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="1"/>
             <c:showCatName val="0"/>
@@ -474,7 +495,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v> 2^15 (32768)      </c:v>
+                  <c:v>2^15 (32768)      </c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -630,7 +651,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v> 2^16 (65536)      </c:v>
+                  <c:v>2^16 (65536)      </c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -786,7 +807,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v> 2^17 (131072)     </c:v>
+                  <c:v>2^17 (131072)     </c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -942,7 +963,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v> 2^18 (262144)     </c:v>
+                  <c:v>2^18 (262144)     </c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1098,7 +1119,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v> 2^19 (524288)     </c:v>
+                  <c:v>2^19 (524288)     </c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1254,7 +1275,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v> 2^20 (1048576)    </c:v>
+                  <c:v>2^20 (1048576)    </c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1412,7 +1433,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v> 2^21 (2097152)    </c:v>
+                  <c:v>2^21 (2097152)    </c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1570,7 +1591,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v> 2^22 (4194304)    </c:v>
+                  <c:v>2^22 (4194304)    </c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1728,7 +1749,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v> 2^23 (8388608)    </c:v>
+                  <c:v>2^23 (8388608)    </c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1886,7 +1907,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v> 2^24 (16777216)   </c:v>
+                  <c:v>2^24 (16777216)   </c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2044,7 +2065,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v> 2^25 (33554432)   </c:v>
+                  <c:v>2^25 (33554432)   </c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2194,9 +2215,8 @@
           </c:extLst>
         </c:ser>
         <c:dLbls>
-          <c:dLblPos val="t"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
+          <c:showVal val="0"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
@@ -2435,7 +2455,7 @@
         <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
         <a:lstStyle/>
         <a:p>
-          <a:pPr>
+          <a:pPr rtl="0">
             <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
@@ -2573,11 +2593,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$63</c:f>
+              <c:f>Sheet1!$A$113</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v> 2^14 (16384)      </c:v>
+                  <c:v>2^14 (16384)      </c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2596,7 +2616,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$B$62:$I$62</c:f>
+              <c:f>Sheet1!$B$112:$I$112</c:f>
               <c:strCache>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
@@ -2628,7 +2648,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$63:$I$63</c:f>
+              <c:f>Sheet1!$B$113:$I$113</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="8"/>
@@ -2671,11 +2691,11 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$64</c:f>
+              <c:f>Sheet1!$A$114</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v> 2^15 (32768)      </c:v>
+                  <c:v>2^15 (32768)      </c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2694,7 +2714,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$B$62:$I$62</c:f>
+              <c:f>Sheet1!$B$112:$I$112</c:f>
               <c:strCache>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
@@ -2726,7 +2746,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$64:$I$64</c:f>
+              <c:f>Sheet1!$B$114:$I$114</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="8"/>
@@ -2769,11 +2789,11 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$65</c:f>
+              <c:f>Sheet1!$A$115</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v> 2^16 (65536)      </c:v>
+                  <c:v>2^16 (65536)      </c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2792,7 +2812,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$B$62:$I$62</c:f>
+              <c:f>Sheet1!$B$112:$I$112</c:f>
               <c:strCache>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
@@ -2824,7 +2844,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$65:$I$65</c:f>
+              <c:f>Sheet1!$B$115:$I$115</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="8"/>
@@ -2867,11 +2887,11 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$66</c:f>
+              <c:f>Sheet1!$A$116</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v> 2^17 (131072)     </c:v>
+                  <c:v>2^17 (131072)     </c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2890,7 +2910,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$B$62:$I$62</c:f>
+              <c:f>Sheet1!$B$112:$I$112</c:f>
               <c:strCache>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
@@ -2922,7 +2942,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$66:$I$66</c:f>
+              <c:f>Sheet1!$B$116:$I$116</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="8"/>
@@ -2965,11 +2985,11 @@
           <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$67</c:f>
+              <c:f>Sheet1!$A$117</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v> 2^18 (262144)     </c:v>
+                  <c:v>2^18 (262144)     </c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2988,7 +3008,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$B$62:$I$62</c:f>
+              <c:f>Sheet1!$B$112:$I$112</c:f>
               <c:strCache>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
@@ -3020,7 +3040,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$67:$I$67</c:f>
+              <c:f>Sheet1!$B$117:$I$117</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="8"/>
@@ -3063,11 +3083,11 @@
           <c:order val="5"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$68</c:f>
+              <c:f>Sheet1!$A$118</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v> 2^19 (524288)     </c:v>
+                  <c:v>2^19 (524288)     </c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3086,7 +3106,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$B$62:$I$62</c:f>
+              <c:f>Sheet1!$B$112:$I$112</c:f>
               <c:strCache>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
@@ -3118,7 +3138,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$68:$I$68</c:f>
+              <c:f>Sheet1!$B$118:$I$118</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="8"/>
@@ -3161,11 +3181,11 @@
           <c:order val="6"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$69</c:f>
+              <c:f>Sheet1!$A$119</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v> 2^20 (1048576)    </c:v>
+                  <c:v>2^20 (1048576)    </c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3186,7 +3206,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$B$62:$I$62</c:f>
+              <c:f>Sheet1!$B$112:$I$112</c:f>
               <c:strCache>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
@@ -3218,7 +3238,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$69:$I$69</c:f>
+              <c:f>Sheet1!$B$119:$I$119</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="8"/>
@@ -3261,11 +3281,11 @@
           <c:order val="7"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$70</c:f>
+              <c:f>Sheet1!$A$120</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v> 2^21 (2097152)    </c:v>
+                  <c:v>2^21 (2097152)    </c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3286,7 +3306,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$B$62:$I$62</c:f>
+              <c:f>Sheet1!$B$112:$I$112</c:f>
               <c:strCache>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
@@ -3318,7 +3338,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$70:$I$70</c:f>
+              <c:f>Sheet1!$B$120:$I$120</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="8"/>
@@ -3361,11 +3381,11 @@
           <c:order val="8"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$71</c:f>
+              <c:f>Sheet1!$A$121</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v> 2^22 (4194304)    </c:v>
+                  <c:v>2^22 (4194304)    </c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3386,7 +3406,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$B$62:$I$62</c:f>
+              <c:f>Sheet1!$B$112:$I$112</c:f>
               <c:strCache>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
@@ -3418,7 +3438,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$71:$I$71</c:f>
+              <c:f>Sheet1!$B$121:$I$121</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="8"/>
@@ -3461,11 +3481,11 @@
           <c:order val="9"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$72</c:f>
+              <c:f>Sheet1!$A$122</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v> 2^23 (8388608)    </c:v>
+                  <c:v>2^23 (8388608)    </c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3486,7 +3506,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$B$62:$I$62</c:f>
+              <c:f>Sheet1!$B$112:$I$112</c:f>
               <c:strCache>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
@@ -3518,7 +3538,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$72:$I$72</c:f>
+              <c:f>Sheet1!$B$122:$I$122</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="8"/>
@@ -3561,11 +3581,11 @@
           <c:order val="10"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$73</c:f>
+              <c:f>Sheet1!$A$123</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v> 2^24 (16777216)   </c:v>
+                  <c:v>2^24 (16777216)   </c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3586,7 +3606,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$B$62:$I$62</c:f>
+              <c:f>Sheet1!$B$112:$I$112</c:f>
               <c:strCache>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
@@ -3618,7 +3638,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$73:$I$73</c:f>
+              <c:f>Sheet1!$B$123:$I$123</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="8"/>
@@ -3661,11 +3681,11 @@
           <c:order val="11"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$A$74</c:f>
+              <c:f>Sheet1!$A$124</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v> 2^25 (33554432)   </c:v>
+                  <c:v>2^25 (33554432)   </c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3686,7 +3706,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$B$62:$I$62</c:f>
+              <c:f>Sheet1!$B$112:$I$112</c:f>
               <c:strCache>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
@@ -3718,7 +3738,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$B$74:$I$74</c:f>
+              <c:f>Sheet1!$B$124:$I$124</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="8"/>
@@ -4050,7 +4070,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$C$62</c:f>
+              <c:f>Sheet1!$C$112</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4076,42 +4096,42 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$A$63:$A$74</c15:sqref>
+                    <c15:sqref>Sheet1!$A$113:$A$124</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>Sheet1!$A$65:$A$74</c:f>
+              <c:f>Sheet1!$A$115:$A$124</c:f>
               <c:strCache>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v> 2^16 (65536)      </c:v>
+                  <c:v>2^16 (65536)      </c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v> 2^17 (131072)     </c:v>
+                  <c:v>2^17 (131072)     </c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v> 2^18 (262144)     </c:v>
+                  <c:v>2^18 (262144)     </c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v> 2^19 (524288)     </c:v>
+                  <c:v>2^19 (524288)     </c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v> 2^20 (1048576)    </c:v>
+                  <c:v>2^20 (1048576)    </c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v> 2^21 (2097152)    </c:v>
+                  <c:v>2^21 (2097152)    </c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v> 2^22 (4194304)    </c:v>
+                  <c:v>2^22 (4194304)    </c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v> 2^23 (8388608)    </c:v>
+                  <c:v>2^23 (8388608)    </c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v> 2^24 (16777216)   </c:v>
+                  <c:v>2^24 (16777216)   </c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v> 2^25 (33554432)   </c:v>
+                  <c:v>2^25 (33554432)   </c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4121,11 +4141,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$C$63:$C$74</c15:sqref>
+                    <c15:sqref>Sheet1!$C$113:$C$124</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>Sheet1!$C$65:$C$74</c:f>
+              <c:f>Sheet1!$C$115:$C$124</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="10"/>
@@ -4174,7 +4194,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$D$62</c:f>
+              <c:f>Sheet1!$D$112</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4200,42 +4220,42 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$A$63:$A$74</c15:sqref>
+                    <c15:sqref>Sheet1!$A$113:$A$124</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>Sheet1!$A$65:$A$74</c:f>
+              <c:f>Sheet1!$A$115:$A$124</c:f>
               <c:strCache>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v> 2^16 (65536)      </c:v>
+                  <c:v>2^16 (65536)      </c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v> 2^17 (131072)     </c:v>
+                  <c:v>2^17 (131072)     </c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v> 2^18 (262144)     </c:v>
+                  <c:v>2^18 (262144)     </c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v> 2^19 (524288)     </c:v>
+                  <c:v>2^19 (524288)     </c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v> 2^20 (1048576)    </c:v>
+                  <c:v>2^20 (1048576)    </c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v> 2^21 (2097152)    </c:v>
+                  <c:v>2^21 (2097152)    </c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v> 2^22 (4194304)    </c:v>
+                  <c:v>2^22 (4194304)    </c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v> 2^23 (8388608)    </c:v>
+                  <c:v>2^23 (8388608)    </c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v> 2^24 (16777216)   </c:v>
+                  <c:v>2^24 (16777216)   </c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v> 2^25 (33554432)   </c:v>
+                  <c:v>2^25 (33554432)   </c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4245,11 +4265,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$D$63:$D$74</c15:sqref>
+                    <c15:sqref>Sheet1!$D$113:$D$124</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>Sheet1!$D$65:$D$74</c:f>
+              <c:f>Sheet1!$D$115:$D$124</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="10"/>
@@ -4298,7 +4318,7 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$E$62</c:f>
+              <c:f>Sheet1!$E$112</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4324,42 +4344,42 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$A$63:$A$74</c15:sqref>
+                    <c15:sqref>Sheet1!$A$113:$A$124</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>Sheet1!$A$65:$A$74</c:f>
+              <c:f>Sheet1!$A$115:$A$124</c:f>
               <c:strCache>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v> 2^16 (65536)      </c:v>
+                  <c:v>2^16 (65536)      </c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v> 2^17 (131072)     </c:v>
+                  <c:v>2^17 (131072)     </c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v> 2^18 (262144)     </c:v>
+                  <c:v>2^18 (262144)     </c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v> 2^19 (524288)     </c:v>
+                  <c:v>2^19 (524288)     </c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v> 2^20 (1048576)    </c:v>
+                  <c:v>2^20 (1048576)    </c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v> 2^21 (2097152)    </c:v>
+                  <c:v>2^21 (2097152)    </c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v> 2^22 (4194304)    </c:v>
+                  <c:v>2^22 (4194304)    </c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v> 2^23 (8388608)    </c:v>
+                  <c:v>2^23 (8388608)    </c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v> 2^24 (16777216)   </c:v>
+                  <c:v>2^24 (16777216)   </c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v> 2^25 (33554432)   </c:v>
+                  <c:v>2^25 (33554432)   </c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4369,11 +4389,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$E$63:$E$74</c15:sqref>
+                    <c15:sqref>Sheet1!$E$113:$E$124</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>Sheet1!$E$65:$E$74</c:f>
+              <c:f>Sheet1!$E$115:$E$124</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="10"/>
@@ -4422,7 +4442,7 @@
           <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$F$62</c:f>
+              <c:f>Sheet1!$F$112</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4448,42 +4468,42 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$A$63:$A$74</c15:sqref>
+                    <c15:sqref>Sheet1!$A$113:$A$124</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>Sheet1!$A$65:$A$74</c:f>
+              <c:f>Sheet1!$A$115:$A$124</c:f>
               <c:strCache>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v> 2^16 (65536)      </c:v>
+                  <c:v>2^16 (65536)      </c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v> 2^17 (131072)     </c:v>
+                  <c:v>2^17 (131072)     </c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v> 2^18 (262144)     </c:v>
+                  <c:v>2^18 (262144)     </c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v> 2^19 (524288)     </c:v>
+                  <c:v>2^19 (524288)     </c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v> 2^20 (1048576)    </c:v>
+                  <c:v>2^20 (1048576)    </c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v> 2^21 (2097152)    </c:v>
+                  <c:v>2^21 (2097152)    </c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v> 2^22 (4194304)    </c:v>
+                  <c:v>2^22 (4194304)    </c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v> 2^23 (8388608)    </c:v>
+                  <c:v>2^23 (8388608)    </c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v> 2^24 (16777216)   </c:v>
+                  <c:v>2^24 (16777216)   </c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v> 2^25 (33554432)   </c:v>
+                  <c:v>2^25 (33554432)   </c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4493,11 +4513,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$F$63:$F$74</c15:sqref>
+                    <c15:sqref>Sheet1!$F$113:$F$124</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>Sheet1!$F$65:$F$74</c:f>
+              <c:f>Sheet1!$F$115:$F$124</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="10"/>
@@ -4546,7 +4566,7 @@
           <c:order val="5"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$G$62</c:f>
+              <c:f>Sheet1!$G$112</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4572,42 +4592,42 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$A$63:$A$74</c15:sqref>
+                    <c15:sqref>Sheet1!$A$113:$A$124</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>Sheet1!$A$65:$A$74</c:f>
+              <c:f>Sheet1!$A$115:$A$124</c:f>
               <c:strCache>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v> 2^16 (65536)      </c:v>
+                  <c:v>2^16 (65536)      </c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v> 2^17 (131072)     </c:v>
+                  <c:v>2^17 (131072)     </c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v> 2^18 (262144)     </c:v>
+                  <c:v>2^18 (262144)     </c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v> 2^19 (524288)     </c:v>
+                  <c:v>2^19 (524288)     </c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v> 2^20 (1048576)    </c:v>
+                  <c:v>2^20 (1048576)    </c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v> 2^21 (2097152)    </c:v>
+                  <c:v>2^21 (2097152)    </c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v> 2^22 (4194304)    </c:v>
+                  <c:v>2^22 (4194304)    </c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v> 2^23 (8388608)    </c:v>
+                  <c:v>2^23 (8388608)    </c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v> 2^24 (16777216)   </c:v>
+                  <c:v>2^24 (16777216)   </c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v> 2^25 (33554432)   </c:v>
+                  <c:v>2^25 (33554432)   </c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4617,11 +4637,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$G$63:$G$74</c15:sqref>
+                    <c15:sqref>Sheet1!$G$113:$G$124</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>Sheet1!$G$65:$G$74</c:f>
+              <c:f>Sheet1!$G$115:$G$124</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="10"/>
@@ -4670,7 +4690,7 @@
           <c:order val="6"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$H$62</c:f>
+              <c:f>Sheet1!$H$112</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4698,42 +4718,42 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$A$63:$A$74</c15:sqref>
+                    <c15:sqref>Sheet1!$A$113:$A$124</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>Sheet1!$A$65:$A$74</c:f>
+              <c:f>Sheet1!$A$115:$A$124</c:f>
               <c:strCache>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v> 2^16 (65536)      </c:v>
+                  <c:v>2^16 (65536)      </c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v> 2^17 (131072)     </c:v>
+                  <c:v>2^17 (131072)     </c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v> 2^18 (262144)     </c:v>
+                  <c:v>2^18 (262144)     </c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v> 2^19 (524288)     </c:v>
+                  <c:v>2^19 (524288)     </c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v> 2^20 (1048576)    </c:v>
+                  <c:v>2^20 (1048576)    </c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v> 2^21 (2097152)    </c:v>
+                  <c:v>2^21 (2097152)    </c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v> 2^22 (4194304)    </c:v>
+                  <c:v>2^22 (4194304)    </c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v> 2^23 (8388608)    </c:v>
+                  <c:v>2^23 (8388608)    </c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v> 2^24 (16777216)   </c:v>
+                  <c:v>2^24 (16777216)   </c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v> 2^25 (33554432)   </c:v>
+                  <c:v>2^25 (33554432)   </c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4743,11 +4763,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$H$63:$H$74</c15:sqref>
+                    <c15:sqref>Sheet1!$H$113:$H$124</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>Sheet1!$H$65:$H$74</c:f>
+              <c:f>Sheet1!$H$115:$H$124</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="10"/>
@@ -4796,7 +4816,7 @@
           <c:order val="7"/>
           <c:tx>
             <c:strRef>
-              <c:f>Sheet1!$I$62</c:f>
+              <c:f>Sheet1!$I$112</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -4824,42 +4844,42 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$A$63:$A$74</c15:sqref>
+                    <c15:sqref>Sheet1!$A$113:$A$124</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>Sheet1!$A$65:$A$74</c:f>
+              <c:f>Sheet1!$A$115:$A$124</c:f>
               <c:strCache>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v> 2^16 (65536)      </c:v>
+                  <c:v>2^16 (65536)      </c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v> 2^17 (131072)     </c:v>
+                  <c:v>2^17 (131072)     </c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v> 2^18 (262144)     </c:v>
+                  <c:v>2^18 (262144)     </c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v> 2^19 (524288)     </c:v>
+                  <c:v>2^19 (524288)     </c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v> 2^20 (1048576)    </c:v>
+                  <c:v>2^20 (1048576)    </c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v> 2^21 (2097152)    </c:v>
+                  <c:v>2^21 (2097152)    </c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v> 2^22 (4194304)    </c:v>
+                  <c:v>2^22 (4194304)    </c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v> 2^23 (8388608)    </c:v>
+                  <c:v>2^23 (8388608)    </c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v> 2^24 (16777216)   </c:v>
+                  <c:v>2^24 (16777216)   </c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v> 2^25 (33554432)   </c:v>
+                  <c:v>2^25 (33554432)   </c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -4869,11 +4889,11 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                   <c15:fullRef>
-                    <c15:sqref>Sheet1!$I$63:$I$74</c15:sqref>
+                    <c15:sqref>Sheet1!$I$113:$I$124</c15:sqref>
                   </c15:fullRef>
                 </c:ext>
               </c:extLst>
-              <c:f>Sheet1!$I$65:$I$74</c:f>
+              <c:f>Sheet1!$I$115:$I$124</c:f>
               <c:numCache>
                 <c:formatCode>0%</c:formatCode>
                 <c:ptCount val="10"/>
@@ -4939,7 +4959,7 @@
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:formulaRef>
-                          <c15:sqref>Sheet1!$B$62</c15:sqref>
+                          <c15:sqref>Sheet1!$B$112</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -4968,44 +4988,44 @@
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:fullRef>
-                          <c15:sqref>Sheet1!$A$63:$A$74</c15:sqref>
+                          <c15:sqref>Sheet1!$A$113:$A$124</c15:sqref>
                         </c15:fullRef>
                         <c15:formulaRef>
-                          <c15:sqref>Sheet1!$A$65:$A$74</c15:sqref>
+                          <c15:sqref>Sheet1!$A$115:$A$124</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
                     <c:strCache>
                       <c:ptCount val="10"/>
                       <c:pt idx="0">
-                        <c:v> 2^16 (65536)      </c:v>
+                        <c:v>2^16 (65536)      </c:v>
                       </c:pt>
                       <c:pt idx="1">
-                        <c:v> 2^17 (131072)     </c:v>
+                        <c:v>2^17 (131072)     </c:v>
                       </c:pt>
                       <c:pt idx="2">
-                        <c:v> 2^18 (262144)     </c:v>
+                        <c:v>2^18 (262144)     </c:v>
                       </c:pt>
                       <c:pt idx="3">
-                        <c:v> 2^19 (524288)     </c:v>
+                        <c:v>2^19 (524288)     </c:v>
                       </c:pt>
                       <c:pt idx="4">
-                        <c:v> 2^20 (1048576)    </c:v>
+                        <c:v>2^20 (1048576)    </c:v>
                       </c:pt>
                       <c:pt idx="5">
-                        <c:v> 2^21 (2097152)    </c:v>
+                        <c:v>2^21 (2097152)    </c:v>
                       </c:pt>
                       <c:pt idx="6">
-                        <c:v> 2^22 (4194304)    </c:v>
+                        <c:v>2^22 (4194304)    </c:v>
                       </c:pt>
                       <c:pt idx="7">
-                        <c:v> 2^23 (8388608)    </c:v>
+                        <c:v>2^23 (8388608)    </c:v>
                       </c:pt>
                       <c:pt idx="8">
-                        <c:v> 2^24 (16777216)   </c:v>
+                        <c:v>2^24 (16777216)   </c:v>
                       </c:pt>
                       <c:pt idx="9">
-                        <c:v> 2^25 (33554432)   </c:v>
+                        <c:v>2^25 (33554432)   </c:v>
                       </c:pt>
                     </c:strCache>
                   </c:strRef>
@@ -5015,10 +5035,10 @@
                     <c:extLst>
                       <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
                         <c15:fullRef>
-                          <c15:sqref>Sheet1!$B$63:$B$74</c15:sqref>
+                          <c15:sqref>Sheet1!$B$113:$B$124</c15:sqref>
                         </c15:fullRef>
                         <c15:formulaRef>
-                          <c15:sqref>Sheet1!$B$65:$B$74</c15:sqref>
+                          <c15:sqref>Sheet1!$B$115:$B$124</c15:sqref>
                         </c15:formulaRef>
                       </c:ext>
                     </c:extLst>
@@ -5259,6 +5279,2957 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="11"/>
+          <c:order val="11"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$A$14</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2^25 (33554432)   </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent6">
+                    <a:lumMod val="60000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="lt-LT"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$B$2:$I$2</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>1 gija</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2 gijos</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3 gijos</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4 gijos</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6 gijos</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>8 gijos</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>16 gijų</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>32 gijos</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$14:$I$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>3920</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2066</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2057</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2061</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1134</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1168</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>720</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>558</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000B-60A6-4A09-B92E-145F5811B2F1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="t"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1273012367"/>
+        <c:axId val="1273012783"/>
+        <c:extLst>
+          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+            <c15:filteredLineSeries>
+              <c15:ser>
+                <c:idx val="0"/>
+                <c:order val="0"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$A$3</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>2^14 (16384)      </c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="28575" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent1"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent1"/>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent1"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:dLbls>
+                  <c:spPr>
+                    <a:noFill/>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                  <c:txPr>
+                    <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                      <a:spAutoFit/>
+                    </a:bodyPr>
+                    <a:lstStyle/>
+                    <a:p>
+                      <a:pPr>
+                        <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                          <a:solidFill>
+                            <a:schemeClr val="tx1">
+                              <a:lumMod val="75000"/>
+                              <a:lumOff val="25000"/>
+                            </a:schemeClr>
+                          </a:solidFill>
+                          <a:latin typeface="+mn-lt"/>
+                          <a:ea typeface="+mn-ea"/>
+                          <a:cs typeface="+mn-cs"/>
+                        </a:defRPr>
+                      </a:pPr>
+                      <a:endParaRPr lang="lt-LT"/>
+                    </a:p>
+                  </c:txPr>
+                  <c:dLblPos val="t"/>
+                  <c:showLegendKey val="0"/>
+                  <c:showVal val="1"/>
+                  <c:showCatName val="0"/>
+                  <c:showSerName val="0"/>
+                  <c:showPercent val="0"/>
+                  <c:showBubbleSize val="0"/>
+                  <c:showLeaderLines val="0"/>
+                  <c:extLst>
+                    <c:ext uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                      <c15:showLeaderLines val="1"/>
+                      <c15:leaderLines>
+                        <c:spPr>
+                          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                            <a:solidFill>
+                              <a:schemeClr val="tx1">
+                                <a:lumMod val="35000"/>
+                                <a:lumOff val="65000"/>
+                              </a:schemeClr>
+                            </a:solidFill>
+                            <a:round/>
+                          </a:ln>
+                          <a:effectLst/>
+                        </c:spPr>
+                      </c15:leaderLines>
+                    </c:ext>
+                  </c:extLst>
+                </c:dLbls>
+                <c:cat>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$B$2:$I$2</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="8"/>
+                      <c:pt idx="0">
+                        <c:v>1 gija</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>2 gijos</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>3 gijos</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>4 gijos</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>6 gijos</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>8 gijos</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>16 gijų</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>32 gijos</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$B$3:$I$3</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="8"/>
+                      <c:pt idx="0">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>0</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>0</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>2</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>4</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:smooth val="0"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000000-60A6-4A09-B92E-145F5811B2F1}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredLineSeries>
+            <c15:filteredLineSeries>
+              <c15:ser>
+                <c:idx val="1"/>
+                <c:order val="1"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$A$4</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>2^15 (32768)      </c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="28575" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent2"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent2"/>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent2"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:dLbls>
+                  <c:spPr>
+                    <a:noFill/>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                  <c:txPr>
+                    <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                      <a:spAutoFit/>
+                    </a:bodyPr>
+                    <a:lstStyle/>
+                    <a:p>
+                      <a:pPr>
+                        <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                          <a:solidFill>
+                            <a:schemeClr val="tx1">
+                              <a:lumMod val="75000"/>
+                              <a:lumOff val="25000"/>
+                            </a:schemeClr>
+                          </a:solidFill>
+                          <a:latin typeface="+mn-lt"/>
+                          <a:ea typeface="+mn-ea"/>
+                          <a:cs typeface="+mn-cs"/>
+                        </a:defRPr>
+                      </a:pPr>
+                      <a:endParaRPr lang="lt-LT"/>
+                    </a:p>
+                  </c:txPr>
+                  <c:dLblPos val="t"/>
+                  <c:showLegendKey val="0"/>
+                  <c:showVal val="1"/>
+                  <c:showCatName val="0"/>
+                  <c:showSerName val="0"/>
+                  <c:showPercent val="0"/>
+                  <c:showBubbleSize val="0"/>
+                  <c:showLeaderLines val="0"/>
+                  <c:extLst>
+                    <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                      <c15:showLeaderLines val="1"/>
+                      <c15:leaderLines>
+                        <c:spPr>
+                          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                            <a:solidFill>
+                              <a:schemeClr val="tx1">
+                                <a:lumMod val="35000"/>
+                                <a:lumOff val="65000"/>
+                              </a:schemeClr>
+                            </a:solidFill>
+                            <a:round/>
+                          </a:ln>
+                          <a:effectLst/>
+                        </c:spPr>
+                      </c15:leaderLines>
+                    </c:ext>
+                  </c:extLst>
+                </c:dLbls>
+                <c:cat>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$B$2:$I$2</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="8"/>
+                      <c:pt idx="0">
+                        <c:v>1 gija</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>2 gijos</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>3 gijos</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>4 gijos</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>6 gijos</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>8 gijos</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>16 gijų</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>32 gijos</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$B$4:$I$4</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="8"/>
+                      <c:pt idx="0">
+                        <c:v>2</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>1</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>2</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>5</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:smooth val="0"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000001-60A6-4A09-B92E-145F5811B2F1}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredLineSeries>
+            <c15:filteredLineSeries>
+              <c15:ser>
+                <c:idx val="2"/>
+                <c:order val="2"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$A$5</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>2^16 (65536)      </c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="28575" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent3"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent3"/>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent3"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:dLbls>
+                  <c:spPr>
+                    <a:noFill/>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                  <c:txPr>
+                    <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                      <a:spAutoFit/>
+                    </a:bodyPr>
+                    <a:lstStyle/>
+                    <a:p>
+                      <a:pPr>
+                        <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                          <a:solidFill>
+                            <a:schemeClr val="tx1">
+                              <a:lumMod val="75000"/>
+                              <a:lumOff val="25000"/>
+                            </a:schemeClr>
+                          </a:solidFill>
+                          <a:latin typeface="+mn-lt"/>
+                          <a:ea typeface="+mn-ea"/>
+                          <a:cs typeface="+mn-cs"/>
+                        </a:defRPr>
+                      </a:pPr>
+                      <a:endParaRPr lang="lt-LT"/>
+                    </a:p>
+                  </c:txPr>
+                  <c:dLblPos val="t"/>
+                  <c:showLegendKey val="0"/>
+                  <c:showVal val="1"/>
+                  <c:showCatName val="0"/>
+                  <c:showSerName val="0"/>
+                  <c:showPercent val="0"/>
+                  <c:showBubbleSize val="0"/>
+                  <c:showLeaderLines val="0"/>
+                  <c:extLst>
+                    <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                      <c15:showLeaderLines val="1"/>
+                      <c15:leaderLines>
+                        <c:spPr>
+                          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                            <a:solidFill>
+                              <a:schemeClr val="tx1">
+                                <a:lumMod val="35000"/>
+                                <a:lumOff val="65000"/>
+                              </a:schemeClr>
+                            </a:solidFill>
+                            <a:round/>
+                          </a:ln>
+                          <a:effectLst/>
+                        </c:spPr>
+                      </c15:leaderLines>
+                    </c:ext>
+                  </c:extLst>
+                </c:dLbls>
+                <c:cat>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$B$2:$I$2</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="8"/>
+                      <c:pt idx="0">
+                        <c:v>1 gija</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>2 gijos</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>3 gijos</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>4 gijos</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>6 gijos</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>8 gijos</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>16 gijų</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>32 gijos</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$B$5:$I$5</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="8"/>
+                      <c:pt idx="0">
+                        <c:v>5</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>3</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>3</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>3</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>2</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>2</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>3</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>3</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:smooth val="0"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000002-60A6-4A09-B92E-145F5811B2F1}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredLineSeries>
+            <c15:filteredLineSeries>
+              <c15:ser>
+                <c:idx val="3"/>
+                <c:order val="3"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$A$6</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>2^17 (131072)     </c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="28575" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent4"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent4"/>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent4"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:dLbls>
+                  <c:spPr>
+                    <a:noFill/>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                  <c:txPr>
+                    <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                      <a:spAutoFit/>
+                    </a:bodyPr>
+                    <a:lstStyle/>
+                    <a:p>
+                      <a:pPr>
+                        <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                          <a:solidFill>
+                            <a:schemeClr val="tx1">
+                              <a:lumMod val="75000"/>
+                              <a:lumOff val="25000"/>
+                            </a:schemeClr>
+                          </a:solidFill>
+                          <a:latin typeface="+mn-lt"/>
+                          <a:ea typeface="+mn-ea"/>
+                          <a:cs typeface="+mn-cs"/>
+                        </a:defRPr>
+                      </a:pPr>
+                      <a:endParaRPr lang="lt-LT"/>
+                    </a:p>
+                  </c:txPr>
+                  <c:dLblPos val="t"/>
+                  <c:showLegendKey val="0"/>
+                  <c:showVal val="1"/>
+                  <c:showCatName val="0"/>
+                  <c:showSerName val="0"/>
+                  <c:showPercent val="0"/>
+                  <c:showBubbleSize val="0"/>
+                  <c:showLeaderLines val="0"/>
+                  <c:extLst>
+                    <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                      <c15:showLeaderLines val="1"/>
+                      <c15:leaderLines>
+                        <c:spPr>
+                          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                            <a:solidFill>
+                              <a:schemeClr val="tx1">
+                                <a:lumMod val="35000"/>
+                                <a:lumOff val="65000"/>
+                              </a:schemeClr>
+                            </a:solidFill>
+                            <a:round/>
+                          </a:ln>
+                          <a:effectLst/>
+                        </c:spPr>
+                      </c15:leaderLines>
+                    </c:ext>
+                  </c:extLst>
+                </c:dLbls>
+                <c:cat>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$B$2:$I$2</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="8"/>
+                      <c:pt idx="0">
+                        <c:v>1 gija</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>2 gijos</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>3 gijos</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>4 gijos</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>6 gijos</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>8 gijos</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>16 gijų</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>32 gijos</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$B$6:$I$6</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="8"/>
+                      <c:pt idx="0">
+                        <c:v>12</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>6</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>6</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>6</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>4</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>4</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>4</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>6</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:smooth val="0"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000003-60A6-4A09-B92E-145F5811B2F1}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredLineSeries>
+            <c15:filteredLineSeries>
+              <c15:ser>
+                <c:idx val="4"/>
+                <c:order val="4"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$A$7</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>2^18 (262144)     </c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="28575" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent5"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent5"/>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent5"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:dLbls>
+                  <c:spPr>
+                    <a:noFill/>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                  <c:txPr>
+                    <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                      <a:spAutoFit/>
+                    </a:bodyPr>
+                    <a:lstStyle/>
+                    <a:p>
+                      <a:pPr>
+                        <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                          <a:solidFill>
+                            <a:schemeClr val="tx1">
+                              <a:lumMod val="75000"/>
+                              <a:lumOff val="25000"/>
+                            </a:schemeClr>
+                          </a:solidFill>
+                          <a:latin typeface="+mn-lt"/>
+                          <a:ea typeface="+mn-ea"/>
+                          <a:cs typeface="+mn-cs"/>
+                        </a:defRPr>
+                      </a:pPr>
+                      <a:endParaRPr lang="lt-LT"/>
+                    </a:p>
+                  </c:txPr>
+                  <c:dLblPos val="t"/>
+                  <c:showLegendKey val="0"/>
+                  <c:showVal val="1"/>
+                  <c:showCatName val="0"/>
+                  <c:showSerName val="0"/>
+                  <c:showPercent val="0"/>
+                  <c:showBubbleSize val="0"/>
+                  <c:showLeaderLines val="0"/>
+                  <c:extLst>
+                    <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                      <c15:showLeaderLines val="1"/>
+                      <c15:leaderLines>
+                        <c:spPr>
+                          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                            <a:solidFill>
+                              <a:schemeClr val="tx1">
+                                <a:lumMod val="35000"/>
+                                <a:lumOff val="65000"/>
+                              </a:schemeClr>
+                            </a:solidFill>
+                            <a:round/>
+                          </a:ln>
+                          <a:effectLst/>
+                        </c:spPr>
+                      </c15:leaderLines>
+                    </c:ext>
+                  </c:extLst>
+                </c:dLbls>
+                <c:cat>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$B$2:$I$2</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="8"/>
+                      <c:pt idx="0">
+                        <c:v>1 gija</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>2 gijos</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>3 gijos</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>4 gijos</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>6 gijos</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>8 gijos</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>16 gijų</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>32 gijos</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$B$7:$I$7</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="8"/>
+                      <c:pt idx="0">
+                        <c:v>23</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>12</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>12</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>12</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>8</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>8</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>7</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>8</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:smooth val="0"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000004-60A6-4A09-B92E-145F5811B2F1}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredLineSeries>
+            <c15:filteredLineSeries>
+              <c15:ser>
+                <c:idx val="5"/>
+                <c:order val="5"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$A$8</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>2^19 (524288)     </c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="28575" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent6"/>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent6"/>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent6"/>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:dLbls>
+                  <c:spPr>
+                    <a:noFill/>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                  <c:txPr>
+                    <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                      <a:spAutoFit/>
+                    </a:bodyPr>
+                    <a:lstStyle/>
+                    <a:p>
+                      <a:pPr>
+                        <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                          <a:solidFill>
+                            <a:schemeClr val="tx1">
+                              <a:lumMod val="75000"/>
+                              <a:lumOff val="25000"/>
+                            </a:schemeClr>
+                          </a:solidFill>
+                          <a:latin typeface="+mn-lt"/>
+                          <a:ea typeface="+mn-ea"/>
+                          <a:cs typeface="+mn-cs"/>
+                        </a:defRPr>
+                      </a:pPr>
+                      <a:endParaRPr lang="lt-LT"/>
+                    </a:p>
+                  </c:txPr>
+                  <c:dLblPos val="t"/>
+                  <c:showLegendKey val="0"/>
+                  <c:showVal val="1"/>
+                  <c:showCatName val="0"/>
+                  <c:showSerName val="0"/>
+                  <c:showPercent val="0"/>
+                  <c:showBubbleSize val="0"/>
+                  <c:showLeaderLines val="0"/>
+                  <c:extLst>
+                    <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                      <c15:showLeaderLines val="1"/>
+                      <c15:leaderLines>
+                        <c:spPr>
+                          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                            <a:solidFill>
+                              <a:schemeClr val="tx1">
+                                <a:lumMod val="35000"/>
+                                <a:lumOff val="65000"/>
+                              </a:schemeClr>
+                            </a:solidFill>
+                            <a:round/>
+                          </a:ln>
+                          <a:effectLst/>
+                        </c:spPr>
+                      </c15:leaderLines>
+                    </c:ext>
+                  </c:extLst>
+                </c:dLbls>
+                <c:cat>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$B$2:$I$2</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="8"/>
+                      <c:pt idx="0">
+                        <c:v>1 gija</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>2 gijos</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>3 gijos</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>4 gijos</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>6 gijos</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>8 gijos</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>16 gijų</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>32 gijos</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$B$8:$I$8</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="8"/>
+                      <c:pt idx="0">
+                        <c:v>54</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>30</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>26</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>29</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>16</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>15</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>12</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>12</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:smooth val="0"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000005-60A6-4A09-B92E-145F5811B2F1}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredLineSeries>
+            <c15:filteredLineSeries>
+              <c15:ser>
+                <c:idx val="6"/>
+                <c:order val="6"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$A$9</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>2^20 (1048576)    </c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="28575" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent1">
+                        <a:lumMod val="60000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent1">
+                        <a:lumMod val="60000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent1">
+                          <a:lumMod val="60000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:dLbls>
+                  <c:spPr>
+                    <a:noFill/>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                  <c:txPr>
+                    <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                      <a:spAutoFit/>
+                    </a:bodyPr>
+                    <a:lstStyle/>
+                    <a:p>
+                      <a:pPr>
+                        <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                          <a:solidFill>
+                            <a:schemeClr val="tx1">
+                              <a:lumMod val="75000"/>
+                              <a:lumOff val="25000"/>
+                            </a:schemeClr>
+                          </a:solidFill>
+                          <a:latin typeface="+mn-lt"/>
+                          <a:ea typeface="+mn-ea"/>
+                          <a:cs typeface="+mn-cs"/>
+                        </a:defRPr>
+                      </a:pPr>
+                      <a:endParaRPr lang="lt-LT"/>
+                    </a:p>
+                  </c:txPr>
+                  <c:dLblPos val="t"/>
+                  <c:showLegendKey val="0"/>
+                  <c:showVal val="1"/>
+                  <c:showCatName val="0"/>
+                  <c:showSerName val="0"/>
+                  <c:showPercent val="0"/>
+                  <c:showBubbleSize val="0"/>
+                  <c:showLeaderLines val="0"/>
+                  <c:extLst>
+                    <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                      <c15:showLeaderLines val="1"/>
+                      <c15:leaderLines>
+                        <c:spPr>
+                          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                            <a:solidFill>
+                              <a:schemeClr val="tx1">
+                                <a:lumMod val="35000"/>
+                                <a:lumOff val="65000"/>
+                              </a:schemeClr>
+                            </a:solidFill>
+                            <a:round/>
+                          </a:ln>
+                          <a:effectLst/>
+                        </c:spPr>
+                      </c15:leaderLines>
+                    </c:ext>
+                  </c:extLst>
+                </c:dLbls>
+                <c:cat>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$B$2:$I$2</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="8"/>
+                      <c:pt idx="0">
+                        <c:v>1 gija</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>2 gijos</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>3 gijos</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>4 gijos</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>6 gijos</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>8 gijos</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>16 gijų</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>32 gijos</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$B$9:$I$9</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="8"/>
+                      <c:pt idx="0">
+                        <c:v>112</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>58</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>53</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>58</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>33</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>34</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>23</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>21</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:smooth val="0"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000006-60A6-4A09-B92E-145F5811B2F1}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredLineSeries>
+            <c15:filteredLineSeries>
+              <c15:ser>
+                <c:idx val="7"/>
+                <c:order val="7"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$A$10</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>2^21 (2097152)    </c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="28575" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent2">
+                        <a:lumMod val="60000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent2">
+                        <a:lumMod val="60000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent2">
+                          <a:lumMod val="60000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:dLbls>
+                  <c:spPr>
+                    <a:noFill/>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                  <c:txPr>
+                    <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                      <a:spAutoFit/>
+                    </a:bodyPr>
+                    <a:lstStyle/>
+                    <a:p>
+                      <a:pPr>
+                        <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                          <a:solidFill>
+                            <a:schemeClr val="tx1">
+                              <a:lumMod val="75000"/>
+                              <a:lumOff val="25000"/>
+                            </a:schemeClr>
+                          </a:solidFill>
+                          <a:latin typeface="+mn-lt"/>
+                          <a:ea typeface="+mn-ea"/>
+                          <a:cs typeface="+mn-cs"/>
+                        </a:defRPr>
+                      </a:pPr>
+                      <a:endParaRPr lang="lt-LT"/>
+                    </a:p>
+                  </c:txPr>
+                  <c:dLblPos val="t"/>
+                  <c:showLegendKey val="0"/>
+                  <c:showVal val="1"/>
+                  <c:showCatName val="0"/>
+                  <c:showSerName val="0"/>
+                  <c:showPercent val="0"/>
+                  <c:showBubbleSize val="0"/>
+                  <c:showLeaderLines val="0"/>
+                  <c:extLst>
+                    <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                      <c15:showLeaderLines val="1"/>
+                      <c15:leaderLines>
+                        <c:spPr>
+                          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                            <a:solidFill>
+                              <a:schemeClr val="tx1">
+                                <a:lumMod val="35000"/>
+                                <a:lumOff val="65000"/>
+                              </a:schemeClr>
+                            </a:solidFill>
+                            <a:round/>
+                          </a:ln>
+                          <a:effectLst/>
+                        </c:spPr>
+                      </c15:leaderLines>
+                    </c:ext>
+                  </c:extLst>
+                </c:dLbls>
+                <c:cat>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$B$2:$I$2</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="8"/>
+                      <c:pt idx="0">
+                        <c:v>1 gija</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>2 gijos</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>3 gijos</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>4 gijos</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>6 gijos</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>8 gijos</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>16 gijų</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>32 gijos</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$B$10:$I$10</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="8"/>
+                      <c:pt idx="0">
+                        <c:v>205</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>111</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>118</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>110</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>68</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>63</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>42</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>35</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:smooth val="0"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000007-60A6-4A09-B92E-145F5811B2F1}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredLineSeries>
+            <c15:filteredLineSeries>
+              <c15:ser>
+                <c:idx val="8"/>
+                <c:order val="8"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$A$11</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>2^22 (4194304)    </c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="28575" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent3">
+                        <a:lumMod val="60000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent3">
+                        <a:lumMod val="60000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent3">
+                          <a:lumMod val="60000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:dLbls>
+                  <c:spPr>
+                    <a:noFill/>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                  <c:txPr>
+                    <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                      <a:spAutoFit/>
+                    </a:bodyPr>
+                    <a:lstStyle/>
+                    <a:p>
+                      <a:pPr>
+                        <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                          <a:solidFill>
+                            <a:schemeClr val="tx1">
+                              <a:lumMod val="75000"/>
+                              <a:lumOff val="25000"/>
+                            </a:schemeClr>
+                          </a:solidFill>
+                          <a:latin typeface="+mn-lt"/>
+                          <a:ea typeface="+mn-ea"/>
+                          <a:cs typeface="+mn-cs"/>
+                        </a:defRPr>
+                      </a:pPr>
+                      <a:endParaRPr lang="lt-LT"/>
+                    </a:p>
+                  </c:txPr>
+                  <c:dLblPos val="t"/>
+                  <c:showLegendKey val="0"/>
+                  <c:showVal val="1"/>
+                  <c:showCatName val="0"/>
+                  <c:showSerName val="0"/>
+                  <c:showPercent val="0"/>
+                  <c:showBubbleSize val="0"/>
+                  <c:showLeaderLines val="0"/>
+                  <c:extLst>
+                    <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                      <c15:showLeaderLines val="1"/>
+                      <c15:leaderLines>
+                        <c:spPr>
+                          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                            <a:solidFill>
+                              <a:schemeClr val="tx1">
+                                <a:lumMod val="35000"/>
+                                <a:lumOff val="65000"/>
+                              </a:schemeClr>
+                            </a:solidFill>
+                            <a:round/>
+                          </a:ln>
+                          <a:effectLst/>
+                        </c:spPr>
+                      </c15:leaderLines>
+                    </c:ext>
+                  </c:extLst>
+                </c:dLbls>
+                <c:cat>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$B$2:$I$2</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="8"/>
+                      <c:pt idx="0">
+                        <c:v>1 gija</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>2 gijos</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>3 gijos</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>4 gijos</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>6 gijos</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>8 gijos</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>16 gijų</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>32 gijos</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$B$11:$I$11</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="8"/>
+                      <c:pt idx="0">
+                        <c:v>429</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>218</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>233</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>220</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>138</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>130</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>82</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>60</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:smooth val="0"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000008-60A6-4A09-B92E-145F5811B2F1}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredLineSeries>
+            <c15:filteredLineSeries>
+              <c15:ser>
+                <c:idx val="9"/>
+                <c:order val="9"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$A$12</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>2^23 (8388608)    </c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="28575" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent4">
+                        <a:lumMod val="60000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent4">
+                        <a:lumMod val="60000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent4">
+                          <a:lumMod val="60000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:dLbls>
+                  <c:spPr>
+                    <a:noFill/>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                  <c:txPr>
+                    <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                      <a:spAutoFit/>
+                    </a:bodyPr>
+                    <a:lstStyle/>
+                    <a:p>
+                      <a:pPr>
+                        <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                          <a:solidFill>
+                            <a:schemeClr val="tx1">
+                              <a:lumMod val="75000"/>
+                              <a:lumOff val="25000"/>
+                            </a:schemeClr>
+                          </a:solidFill>
+                          <a:latin typeface="+mn-lt"/>
+                          <a:ea typeface="+mn-ea"/>
+                          <a:cs typeface="+mn-cs"/>
+                        </a:defRPr>
+                      </a:pPr>
+                      <a:endParaRPr lang="lt-LT"/>
+                    </a:p>
+                  </c:txPr>
+                  <c:dLblPos val="t"/>
+                  <c:showLegendKey val="0"/>
+                  <c:showVal val="1"/>
+                  <c:showCatName val="0"/>
+                  <c:showSerName val="0"/>
+                  <c:showPercent val="0"/>
+                  <c:showBubbleSize val="0"/>
+                  <c:showLeaderLines val="0"/>
+                  <c:extLst>
+                    <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                      <c15:showLeaderLines val="1"/>
+                      <c15:leaderLines>
+                        <c:spPr>
+                          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                            <a:solidFill>
+                              <a:schemeClr val="tx1">
+                                <a:lumMod val="35000"/>
+                                <a:lumOff val="65000"/>
+                              </a:schemeClr>
+                            </a:solidFill>
+                            <a:round/>
+                          </a:ln>
+                          <a:effectLst/>
+                        </c:spPr>
+                      </c15:leaderLines>
+                    </c:ext>
+                  </c:extLst>
+                </c:dLbls>
+                <c:cat>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$B$2:$I$2</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="8"/>
+                      <c:pt idx="0">
+                        <c:v>1 gija</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>2 gijos</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>3 gijos</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>4 gijos</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>6 gijos</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>8 gijos</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>16 gijų</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>32 gijos</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$B$12:$I$12</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="8"/>
+                      <c:pt idx="0">
+                        <c:v>940</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>501</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>481</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>505</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>271</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>282</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>175</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>129</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:smooth val="0"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000009-60A6-4A09-B92E-145F5811B2F1}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredLineSeries>
+            <c15:filteredLineSeries>
+              <c15:ser>
+                <c:idx val="10"/>
+                <c:order val="10"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$A$13</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>2^24 (16777216)   </c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:ln w="28575" cap="rnd">
+                    <a:solidFill>
+                      <a:schemeClr val="accent5">
+                        <a:lumMod val="60000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:round/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:marker>
+                  <c:symbol val="circle"/>
+                  <c:size val="5"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent5">
+                        <a:lumMod val="60000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="accent5">
+                          <a:lumMod val="60000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:marker>
+                <c:dLbls>
+                  <c:spPr>
+                    <a:noFill/>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                  <c:txPr>
+                    <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                      <a:spAutoFit/>
+                    </a:bodyPr>
+                    <a:lstStyle/>
+                    <a:p>
+                      <a:pPr>
+                        <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                          <a:solidFill>
+                            <a:schemeClr val="tx1">
+                              <a:lumMod val="75000"/>
+                              <a:lumOff val="25000"/>
+                            </a:schemeClr>
+                          </a:solidFill>
+                          <a:latin typeface="+mn-lt"/>
+                          <a:ea typeface="+mn-ea"/>
+                          <a:cs typeface="+mn-cs"/>
+                        </a:defRPr>
+                      </a:pPr>
+                      <a:endParaRPr lang="lt-LT"/>
+                    </a:p>
+                  </c:txPr>
+                  <c:dLblPos val="t"/>
+                  <c:showLegendKey val="0"/>
+                  <c:showVal val="1"/>
+                  <c:showCatName val="0"/>
+                  <c:showSerName val="0"/>
+                  <c:showPercent val="0"/>
+                  <c:showBubbleSize val="0"/>
+                  <c:showLeaderLines val="0"/>
+                  <c:extLst>
+                    <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                      <c15:showLeaderLines val="1"/>
+                      <c15:leaderLines>
+                        <c:spPr>
+                          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                            <a:solidFill>
+                              <a:schemeClr val="tx1">
+                                <a:lumMod val="35000"/>
+                                <a:lumOff val="65000"/>
+                              </a:schemeClr>
+                            </a:solidFill>
+                            <a:round/>
+                          </a:ln>
+                          <a:effectLst/>
+                        </c:spPr>
+                      </c15:leaderLines>
+                    </c:ext>
+                  </c:extLst>
+                </c:dLbls>
+                <c:cat>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$B$2:$I$2</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="8"/>
+                      <c:pt idx="0">
+                        <c:v>1 gija</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>2 gijos</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>3 gijos</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>4 gijos</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>6 gijos</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>8 gijos</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>16 gijų</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>32 gijos</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>Sheet1!$B$13:$I$13</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="8"/>
+                      <c:pt idx="0">
+                        <c:v>1941</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>1005</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>978</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>999</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>560</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>557</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>353</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>269</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:smooth val="0"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{0000000A-60A6-4A09-B92E-145F5811B2F1}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredLineSeries>
+          </c:ext>
+        </c:extLst>
+      </c:lineChart>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="12"/>
+          <c:order val="12"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$A$15</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>2^25 idealus</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="80000"/>
+                    <a:lumOff val="20000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="lt-LT"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="t"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$B$2:$I$2</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>1 gija</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2 gijos</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3 gijos</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4 gijos</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6 gijos</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>8 gijos</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>16 gijų</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>32 gijos</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$15:$I$15</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>3920</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1960</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1306.6666666666667</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>980</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>653.33333333333337</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>490</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>245</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>122.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000C-60A6-4A09-B92E-145F5811B2F1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="t"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1068942304"/>
+        <c:axId val="1068924832"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1273012367"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="lt-LT"/>
+                  <a:t>R</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>eal</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="lt-LT"/>
+                  <a:t>us</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="lt-LT" baseline="0"/>
+                  <a:t> greitis vs idealus</a:t>
+                </a:r>
+                <a:endParaRPr lang="lt-LT"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="lt-LT"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="lt-LT"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1273012783"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1273012783"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>ms</a:t>
+                </a:r>
+                <a:endParaRPr lang="lt-LT"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="lt-LT"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="lt-LT"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1273012367"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="1068924832"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="r"/>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="lt-LT"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1068942304"/>
+        <c:crosses val="max"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:catAx>
+        <c:axId val="1068942304"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="t"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="lt-LT"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1068924832"/>
+        <c:crosses val="max"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:dTable>
+        <c:showHorzBorder val="1"/>
+        <c:showVertBorder val="1"/>
+        <c:showOutline val="1"/>
+        <c:showKeys val="1"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr rtl="0">
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="lt-LT"/>
+          </a:p>
+        </c:txPr>
+      </c:dTable>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr rtl="0">
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="lt-LT"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="lt-LT"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -5340,6 +8311,46 @@
 </file>
 
 <file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -6927,19 +9938,535 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>257175</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>142875</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>57</xdr:row>
+      <xdr:row>59</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -6969,13 +10496,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>180975</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>126</xdr:row>
       <xdr:rowOff>119062</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>104</xdr:row>
+      <xdr:row>154</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -7005,13 +10532,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>219075</xdr:colOff>
-      <xdr:row>105</xdr:row>
+      <xdr:row>155</xdr:row>
       <xdr:rowOff>142875</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>85725</xdr:colOff>
-      <xdr:row>133</xdr:row>
+      <xdr:row>183</xdr:row>
       <xdr:rowOff>138113</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -7034,6 +10561,44 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>238126</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>66676</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{49CEEA5F-5A98-419D-9234-6EB62993EFAE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -7339,7 +10904,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CFCCE9D-6F94-40D3-99CD-016EDD3ED3FF}">
-  <dimension ref="A1:I74"/>
+  <dimension ref="A1:J125"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
@@ -7353,897 +10918,982 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
+      <c r="A1" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="G2" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="I2" s="10" t="s">
-        <v>20</v>
+      <c r="B2" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3">
         <v>1</v>
       </c>
-      <c r="B3" s="5">
+      <c r="C3">
         <v>1</v>
       </c>
-      <c r="C3" s="5">
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
         <v>1</v>
       </c>
-      <c r="D3" s="5">
-        <v>0</v>
-      </c>
-      <c r="E3" s="5">
-        <v>0</v>
-      </c>
-      <c r="F3" s="5">
+      <c r="G3">
         <v>1</v>
       </c>
-      <c r="G3" s="5">
-        <v>1</v>
-      </c>
-      <c r="H3" s="5">
+      <c r="H3">
         <v>2</v>
       </c>
-      <c r="I3" s="6">
+      <c r="I3" s="5">
         <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4">
         <v>2</v>
       </c>
-      <c r="B4" s="5">
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
         <v>2</v>
       </c>
-      <c r="C4" s="5">
-        <v>1</v>
-      </c>
-      <c r="D4" s="5">
-        <v>1</v>
-      </c>
-      <c r="E4" s="5">
-        <v>1</v>
-      </c>
-      <c r="F4" s="5">
-        <v>1</v>
-      </c>
-      <c r="G4" s="5">
-        <v>1</v>
-      </c>
-      <c r="H4" s="5">
-        <v>2</v>
-      </c>
-      <c r="I4" s="6">
+      <c r="I4" s="5">
         <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+      <c r="C5">
         <v>3</v>
       </c>
-      <c r="B5" s="5">
-        <v>5</v>
-      </c>
-      <c r="C5" s="5">
+      <c r="D5">
         <v>3</v>
       </c>
-      <c r="D5" s="5">
+      <c r="E5">
         <v>3</v>
       </c>
-      <c r="E5" s="5">
+      <c r="F5">
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+      <c r="H5">
         <v>3</v>
       </c>
-      <c r="F5" s="5">
-        <v>2</v>
-      </c>
-      <c r="G5" s="5">
-        <v>2</v>
-      </c>
-      <c r="H5" s="5">
-        <v>3</v>
-      </c>
-      <c r="I5" s="6">
+      <c r="I5" s="5">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6">
+        <v>12</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+      <c r="D6">
+        <v>6</v>
+      </c>
+      <c r="E6">
+        <v>6</v>
+      </c>
+      <c r="F6">
         <v>4</v>
       </c>
-      <c r="B6" s="5">
-        <v>12</v>
-      </c>
-      <c r="C6" s="5">
-        <v>6</v>
-      </c>
-      <c r="D6" s="5">
-        <v>6</v>
-      </c>
-      <c r="E6" s="5">
-        <v>6</v>
-      </c>
-      <c r="F6" s="5">
+      <c r="G6">
         <v>4</v>
       </c>
-      <c r="G6" s="5">
+      <c r="H6">
         <v>4</v>
       </c>
-      <c r="H6" s="5">
-        <v>4</v>
-      </c>
-      <c r="I6" s="6">
+      <c r="I6" s="5">
         <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="5">
+      <c r="A7" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7">
         <v>23</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7">
         <v>12</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7">
         <v>12</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7">
         <v>12</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7">
         <v>8</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7">
         <v>8</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7">
         <v>7</v>
       </c>
-      <c r="I7" s="6">
+      <c r="I7" s="5">
         <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="5">
+      <c r="A8" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8">
         <v>54</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8">
         <v>30</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8">
         <v>26</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8">
         <v>29</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F8">
         <v>16</v>
       </c>
-      <c r="G8" s="5">
+      <c r="G8">
         <v>15</v>
       </c>
-      <c r="H8" s="5">
+      <c r="H8">
         <v>12</v>
       </c>
-      <c r="I8" s="6">
+      <c r="I8" s="5">
         <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="5">
+      <c r="A9" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9">
         <v>112</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9">
         <v>58</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9">
         <v>53</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9">
         <v>58</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F9">
         <v>33</v>
       </c>
-      <c r="G9" s="5">
+      <c r="G9">
         <v>34</v>
       </c>
-      <c r="H9" s="5">
+      <c r="H9">
         <v>23</v>
       </c>
-      <c r="I9" s="6">
+      <c r="I9" s="5">
         <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="5">
+      <c r="A10" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10">
         <v>205</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10">
         <v>111</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10">
         <v>118</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10">
         <v>110</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F10">
         <v>68</v>
       </c>
-      <c r="G10" s="5">
+      <c r="G10">
         <v>63</v>
       </c>
-      <c r="H10" s="5">
+      <c r="H10">
         <v>42</v>
       </c>
-      <c r="I10" s="6">
+      <c r="I10" s="5">
         <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="5">
+      <c r="A11" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11">
         <v>429</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11">
         <v>218</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11">
         <v>233</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11">
         <v>220</v>
       </c>
-      <c r="F11" s="5">
+      <c r="F11">
         <v>138</v>
       </c>
-      <c r="G11" s="5">
+      <c r="G11">
         <v>130</v>
       </c>
-      <c r="H11" s="5">
+      <c r="H11">
         <v>82</v>
       </c>
-      <c r="I11" s="6">
+      <c r="I11" s="5">
         <v>60</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" s="5">
+      <c r="A12" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12">
         <v>940</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12">
         <v>501</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12">
         <v>481</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12">
         <v>505</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F12">
         <v>271</v>
       </c>
-      <c r="G12" s="5">
+      <c r="G12">
         <v>282</v>
       </c>
-      <c r="H12" s="5">
+      <c r="H12">
         <v>175</v>
       </c>
-      <c r="I12" s="6">
+      <c r="I12" s="5">
         <v>129</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" s="5">
+      <c r="A13" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13">
         <v>1941</v>
       </c>
-      <c r="C13" s="5">
+      <c r="C13">
         <v>1005</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D13">
         <v>978</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13">
         <v>999</v>
       </c>
-      <c r="F13" s="5">
+      <c r="F13">
         <v>560</v>
       </c>
-      <c r="G13" s="5">
+      <c r="G13">
         <v>557</v>
       </c>
-      <c r="H13" s="5">
+      <c r="H13">
         <v>353</v>
       </c>
-      <c r="I13" s="6">
+      <c r="I13" s="5">
         <v>269</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" s="7">
+      <c r="A14" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="6">
         <v>3920</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="6">
         <v>2066</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="6">
         <v>2057</v>
       </c>
-      <c r="E14" s="7">
+      <c r="E14" s="6">
         <v>2061</v>
       </c>
-      <c r="F14" s="7">
+      <c r="F14" s="6">
         <v>1134</v>
       </c>
-      <c r="G14" s="7">
+      <c r="G14" s="6">
         <v>1168</v>
       </c>
-      <c r="H14" s="7">
+      <c r="H14" s="6">
         <v>720</v>
       </c>
-      <c r="I14" s="8">
+      <c r="I14" s="7">
         <v>558</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A61" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B61" s="9"/>
-      <c r="C61" s="9"/>
-      <c r="D61" s="9"/>
-      <c r="E61" s="9"/>
-      <c r="F61" s="9"/>
-      <c r="G61" s="9"/>
-      <c r="H61" s="9"/>
-      <c r="I61" s="9"/>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="20">
+        <f>$B$14</f>
+        <v>3920</v>
+      </c>
+      <c r="C15" s="21">
+        <f>$B$15/2</f>
+        <v>1960</v>
+      </c>
+      <c r="D15" s="21">
+        <f>$B$15/3</f>
+        <v>1306.6666666666667</v>
+      </c>
+      <c r="E15" s="21">
+        <f>$B$15/4</f>
+        <v>980</v>
+      </c>
+      <c r="F15" s="21">
+        <f>$B$15/6</f>
+        <v>653.33333333333337</v>
+      </c>
+      <c r="G15" s="21">
+        <f>$B$15/8</f>
+        <v>490</v>
+      </c>
+      <c r="H15" s="21">
+        <f>$B$15/16</f>
+        <v>245</v>
+      </c>
+      <c r="I15" s="22">
+        <f>$B$15/32</f>
+        <v>122.5</v>
+      </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A62" s="14" t="str">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A111" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B111" s="14"/>
+      <c r="C111" s="14"/>
+      <c r="D111" s="14"/>
+      <c r="E111" s="14"/>
+      <c r="F111" s="14"/>
+      <c r="G111" s="14"/>
+      <c r="H111" s="14"/>
+      <c r="I111" s="14"/>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A112" s="8" t="str">
         <f>A2</f>
         <v xml:space="preserve"> Masyvo dydis      </v>
       </c>
-      <c r="B62" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="C62" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="D62" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="E62" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="F62" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="G62" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="H62" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="I62" s="14" t="s">
-        <v>20</v>
+      <c r="B112" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C112" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D112" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="E112" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="F112" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="G112" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="H112" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="I112" s="8" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A63" s="12" t="str">
-        <f t="shared" ref="A63" si="0">A3</f>
-        <v xml:space="preserve"> 2^14 (16384)      </v>
-      </c>
-      <c r="B63" s="1">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A113" s="11" t="str">
+        <f>A3</f>
+        <v xml:space="preserve">2^14 (16384)      </v>
+      </c>
+      <c r="B113" s="1">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="C63" s="1">
+      <c r="C113" s="1">
         <f>IF(AND($B3&gt;0),(C3-$B3)/$B3,0)</f>
         <v>0</v>
       </c>
-      <c r="D63" s="1">
-        <f t="shared" ref="D63:I63" si="1">IF(AND($B3&gt;0),(D3-$B3)/$B3,0)</f>
+      <c r="D113" s="1">
+        <f>IF(AND($B3&gt;0),(D3-$B3)/$B3,0)</f>
         <v>-1</v>
       </c>
-      <c r="E63" s="1">
-        <f t="shared" si="1"/>
+      <c r="E113" s="1">
+        <f>IF(AND($B3&gt;0),(E3-$B3)/$B3,0)</f>
         <v>-1</v>
       </c>
-      <c r="F63" s="1">
-        <f t="shared" si="1"/>
+      <c r="F113" s="1">
+        <f>IF(AND($B3&gt;0),(F3-$B3)/$B3,0)</f>
         <v>0</v>
       </c>
-      <c r="G63" s="1">
-        <f t="shared" si="1"/>
+      <c r="G113" s="1">
+        <f>IF(AND($B3&gt;0),(G3-$B3)/$B3,0)</f>
         <v>0</v>
       </c>
-      <c r="H63" s="1">
-        <f t="shared" si="1"/>
+      <c r="H113" s="1">
+        <f>IF(AND($B3&gt;0),(H3-$B3)/$B3,0)</f>
         <v>1</v>
       </c>
-      <c r="I63" s="2">
-        <f t="shared" si="1"/>
+      <c r="I113" s="17">
+        <f>IF(AND($B3&gt;0),(I3-$B3)/$B3,0)</f>
         <v>3</v>
       </c>
+      <c r="J113" s="16"/>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A64" s="12" t="str">
-        <f t="shared" ref="A64" si="2">A4</f>
-        <v xml:space="preserve"> 2^15 (32768)      </v>
-      </c>
-      <c r="B64" s="1">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A114" s="11" t="str">
+        <f>A4</f>
+        <v xml:space="preserve">2^15 (32768)      </v>
+      </c>
+      <c r="B114" s="1">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="C64" s="1">
-        <f t="shared" ref="C64:I74" si="3">IF(AND($B4&gt;0),(C4-$B4)/$B4,0)</f>
+      <c r="C114" s="1">
+        <f>IF(AND($B4&gt;0),(C4-$B4)/$B4,0)</f>
         <v>-0.5</v>
       </c>
-      <c r="D64" s="1">
-        <f t="shared" si="3"/>
+      <c r="D114" s="1">
+        <f>IF(AND($B4&gt;0),(D4-$B4)/$B4,0)</f>
         <v>-0.5</v>
       </c>
-      <c r="E64" s="1">
-        <f t="shared" si="3"/>
+      <c r="E114" s="1">
+        <f>IF(AND($B4&gt;0),(E4-$B4)/$B4,0)</f>
         <v>-0.5</v>
       </c>
-      <c r="F64" s="1">
-        <f t="shared" si="3"/>
+      <c r="F114" s="1">
+        <f>IF(AND($B4&gt;0),(F4-$B4)/$B4,0)</f>
         <v>-0.5</v>
       </c>
-      <c r="G64" s="1">
-        <f t="shared" si="3"/>
+      <c r="G114" s="1">
+        <f>IF(AND($B4&gt;0),(G4-$B4)/$B4,0)</f>
         <v>-0.5</v>
       </c>
-      <c r="H64" s="1">
-        <f t="shared" si="3"/>
+      <c r="H114" s="1">
+        <f>IF(AND($B4&gt;0),(H4-$B4)/$B4,0)</f>
         <v>0</v>
       </c>
-      <c r="I64" s="2">
-        <f t="shared" si="3"/>
+      <c r="I114" s="2">
+        <f>IF(AND($B4&gt;0),(I4-$B4)/$B4,0)</f>
         <v>1.5</v>
       </c>
+      <c r="J114" s="16"/>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A65" s="12" t="str">
-        <f t="shared" ref="A65" si="4">A5</f>
-        <v xml:space="preserve"> 2^16 (65536)      </v>
-      </c>
-      <c r="B65" s="1">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A115" s="11" t="str">
+        <f>A5</f>
+        <v xml:space="preserve">2^16 (65536)      </v>
+      </c>
+      <c r="B115" s="1">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="C65" s="1">
-        <f t="shared" si="3"/>
+      <c r="C115" s="1">
+        <f>IF(AND($B5&gt;0),(C5-$B5)/$B5,0)</f>
         <v>-0.4</v>
       </c>
-      <c r="D65" s="1">
-        <f t="shared" si="3"/>
+      <c r="D115" s="1">
+        <f>IF(AND($B5&gt;0),(D5-$B5)/$B5,0)</f>
         <v>-0.4</v>
       </c>
-      <c r="E65" s="1">
-        <f t="shared" si="3"/>
+      <c r="E115" s="1">
+        <f>IF(AND($B5&gt;0),(E5-$B5)/$B5,0)</f>
         <v>-0.4</v>
       </c>
-      <c r="F65" s="1">
-        <f t="shared" si="3"/>
+      <c r="F115" s="1">
+        <f>IF(AND($B5&gt;0),(F5-$B5)/$B5,0)</f>
         <v>-0.6</v>
       </c>
-      <c r="G65" s="1">
-        <f t="shared" si="3"/>
+      <c r="G115" s="1">
+        <f>IF(AND($B5&gt;0),(G5-$B5)/$B5,0)</f>
         <v>-0.6</v>
       </c>
-      <c r="H65" s="1">
-        <f t="shared" si="3"/>
+      <c r="H115" s="1">
+        <f>IF(AND($B5&gt;0),(H5-$B5)/$B5,0)</f>
         <v>-0.4</v>
       </c>
-      <c r="I65" s="2">
-        <f t="shared" si="3"/>
+      <c r="I115" s="2">
+        <f>IF(AND($B5&gt;0),(I5-$B5)/$B5,0)</f>
         <v>-0.4</v>
       </c>
+      <c r="J115" s="16"/>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A66" s="12" t="str">
-        <f t="shared" ref="A66" si="5">A6</f>
-        <v xml:space="preserve"> 2^17 (131072)     </v>
-      </c>
-      <c r="B66" s="1">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A116" s="11" t="str">
+        <f>A6</f>
+        <v xml:space="preserve">2^17 (131072)     </v>
+      </c>
+      <c r="B116" s="1">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="C66" s="1">
-        <f t="shared" si="3"/>
+      <c r="C116" s="1">
+        <f>IF(AND($B6&gt;0),(C6-$B6)/$B6,0)</f>
         <v>-0.5</v>
       </c>
-      <c r="D66" s="1">
-        <f t="shared" si="3"/>
+      <c r="D116" s="1">
+        <f>IF(AND($B6&gt;0),(D6-$B6)/$B6,0)</f>
         <v>-0.5</v>
       </c>
-      <c r="E66" s="1">
-        <f t="shared" si="3"/>
+      <c r="E116" s="1">
+        <f>IF(AND($B6&gt;0),(E6-$B6)/$B6,0)</f>
         <v>-0.5</v>
       </c>
-      <c r="F66" s="1">
-        <f t="shared" si="3"/>
+      <c r="F116" s="1">
+        <f>IF(AND($B6&gt;0),(F6-$B6)/$B6,0)</f>
         <v>-0.66666666666666663</v>
       </c>
-      <c r="G66" s="1">
-        <f t="shared" si="3"/>
+      <c r="G116" s="1">
+        <f>IF(AND($B6&gt;0),(G6-$B6)/$B6,0)</f>
         <v>-0.66666666666666663</v>
       </c>
-      <c r="H66" s="1">
-        <f t="shared" si="3"/>
+      <c r="H116" s="1">
+        <f>IF(AND($B6&gt;0),(H6-$B6)/$B6,0)</f>
         <v>-0.66666666666666663</v>
       </c>
-      <c r="I66" s="2">
-        <f t="shared" si="3"/>
+      <c r="I116" s="2">
+        <f>IF(AND($B6&gt;0),(I6-$B6)/$B6,0)</f>
         <v>-0.5</v>
       </c>
+      <c r="J116" s="16"/>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A67" s="12" t="str">
-        <f t="shared" ref="A67" si="6">A7</f>
-        <v xml:space="preserve"> 2^18 (262144)     </v>
-      </c>
-      <c r="B67" s="1">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A117" s="11" t="str">
+        <f>A7</f>
+        <v xml:space="preserve">2^18 (262144)     </v>
+      </c>
+      <c r="B117" s="1">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="C67" s="1">
-        <f t="shared" si="3"/>
+      <c r="C117" s="1">
+        <f>IF(AND($B7&gt;0),(C7-$B7)/$B7,0)</f>
         <v>-0.47826086956521741</v>
       </c>
-      <c r="D67" s="1">
-        <f t="shared" si="3"/>
+      <c r="D117" s="1">
+        <f>IF(AND($B7&gt;0),(D7-$B7)/$B7,0)</f>
         <v>-0.47826086956521741</v>
       </c>
-      <c r="E67" s="1">
-        <f t="shared" si="3"/>
+      <c r="E117" s="1">
+        <f>IF(AND($B7&gt;0),(E7-$B7)/$B7,0)</f>
         <v>-0.47826086956521741</v>
       </c>
-      <c r="F67" s="1">
-        <f t="shared" si="3"/>
+      <c r="F117" s="1">
+        <f>IF(AND($B7&gt;0),(F7-$B7)/$B7,0)</f>
         <v>-0.65217391304347827</v>
       </c>
-      <c r="G67" s="1">
-        <f t="shared" si="3"/>
+      <c r="G117" s="1">
+        <f>IF(AND($B7&gt;0),(G7-$B7)/$B7,0)</f>
         <v>-0.65217391304347827</v>
       </c>
-      <c r="H67" s="1">
-        <f t="shared" si="3"/>
+      <c r="H117" s="1">
+        <f>IF(AND($B7&gt;0),(H7-$B7)/$B7,0)</f>
         <v>-0.69565217391304346</v>
       </c>
-      <c r="I67" s="2">
-        <f t="shared" si="3"/>
+      <c r="I117" s="2">
+        <f>IF(AND($B7&gt;0),(I7-$B7)/$B7,0)</f>
         <v>-0.65217391304347827</v>
       </c>
+      <c r="J117" s="16"/>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A68" s="12" t="str">
-        <f t="shared" ref="A68" si="7">A8</f>
-        <v xml:space="preserve"> 2^19 (524288)     </v>
-      </c>
-      <c r="B68" s="1">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A118" s="11" t="str">
+        <f>A8</f>
+        <v xml:space="preserve">2^19 (524288)     </v>
+      </c>
+      <c r="B118" s="1">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="C68" s="1">
-        <f t="shared" si="3"/>
+      <c r="C118" s="1">
+        <f>IF(AND($B8&gt;0),(C8-$B8)/$B8,0)</f>
         <v>-0.44444444444444442</v>
       </c>
-      <c r="D68" s="1">
-        <f t="shared" si="3"/>
+      <c r="D118" s="1">
+        <f>IF(AND($B8&gt;0),(D8-$B8)/$B8,0)</f>
         <v>-0.51851851851851849</v>
       </c>
-      <c r="E68" s="1">
-        <f t="shared" si="3"/>
+      <c r="E118" s="1">
+        <f>IF(AND($B8&gt;0),(E8-$B8)/$B8,0)</f>
         <v>-0.46296296296296297</v>
       </c>
-      <c r="F68" s="1">
-        <f t="shared" si="3"/>
+      <c r="F118" s="1">
+        <f>IF(AND($B8&gt;0),(F8-$B8)/$B8,0)</f>
         <v>-0.70370370370370372</v>
       </c>
-      <c r="G68" s="1">
-        <f t="shared" si="3"/>
+      <c r="G118" s="1">
+        <f>IF(AND($B8&gt;0),(G8-$B8)/$B8,0)</f>
         <v>-0.72222222222222221</v>
       </c>
-      <c r="H68" s="1">
-        <f t="shared" si="3"/>
+      <c r="H118" s="1">
+        <f>IF(AND($B8&gt;0),(H8-$B8)/$B8,0)</f>
         <v>-0.77777777777777779</v>
       </c>
-      <c r="I68" s="2">
-        <f t="shared" si="3"/>
+      <c r="I118" s="2">
+        <f>IF(AND($B8&gt;0),(I8-$B8)/$B8,0)</f>
         <v>-0.77777777777777779</v>
       </c>
+      <c r="J118" s="16"/>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A69" s="12" t="str">
-        <f t="shared" ref="A69" si="8">A9</f>
-        <v xml:space="preserve"> 2^20 (1048576)    </v>
-      </c>
-      <c r="B69" s="1">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A119" s="11" t="str">
+        <f>A9</f>
+        <v xml:space="preserve">2^20 (1048576)    </v>
+      </c>
+      <c r="B119" s="1">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="C69" s="1">
-        <f t="shared" si="3"/>
+      <c r="C119" s="1">
+        <f>IF(AND($B9&gt;0),(C9-$B9)/$B9,0)</f>
         <v>-0.48214285714285715</v>
       </c>
-      <c r="D69" s="1">
-        <f t="shared" si="3"/>
+      <c r="D119" s="1">
+        <f>IF(AND($B9&gt;0),(D9-$B9)/$B9,0)</f>
         <v>-0.5267857142857143</v>
       </c>
-      <c r="E69" s="1">
-        <f t="shared" si="3"/>
+      <c r="E119" s="1">
+        <f>IF(AND($B9&gt;0),(E9-$B9)/$B9,0)</f>
         <v>-0.48214285714285715</v>
       </c>
-      <c r="F69" s="1">
-        <f t="shared" si="3"/>
+      <c r="F119" s="1">
+        <f>IF(AND($B9&gt;0),(F9-$B9)/$B9,0)</f>
         <v>-0.7053571428571429</v>
       </c>
-      <c r="G69" s="1">
-        <f t="shared" si="3"/>
+      <c r="G119" s="1">
+        <f>IF(AND($B9&gt;0),(G9-$B9)/$B9,0)</f>
         <v>-0.6964285714285714</v>
       </c>
-      <c r="H69" s="1">
-        <f t="shared" si="3"/>
+      <c r="H119" s="1">
+        <f>IF(AND($B9&gt;0),(H9-$B9)/$B9,0)</f>
         <v>-0.7946428571428571</v>
       </c>
-      <c r="I69" s="2">
-        <f t="shared" si="3"/>
+      <c r="I119" s="2">
+        <f>IF(AND($B9&gt;0),(I9-$B9)/$B9,0)</f>
         <v>-0.8125</v>
       </c>
+      <c r="J119" s="16"/>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A70" s="12" t="str">
-        <f t="shared" ref="A70" si="9">A10</f>
-        <v xml:space="preserve"> 2^21 (2097152)    </v>
-      </c>
-      <c r="B70" s="1">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A120" s="11" t="str">
+        <f>A10</f>
+        <v xml:space="preserve">2^21 (2097152)    </v>
+      </c>
+      <c r="B120" s="1">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="C70" s="1">
-        <f t="shared" si="3"/>
+      <c r="C120" s="1">
+        <f>IF(AND($B10&gt;0),(C10-$B10)/$B10,0)</f>
         <v>-0.45853658536585368</v>
       </c>
-      <c r="D70" s="1">
-        <f t="shared" si="3"/>
+      <c r="D120" s="1">
+        <f>IF(AND($B10&gt;0),(D10-$B10)/$B10,0)</f>
         <v>-0.42439024390243901</v>
       </c>
-      <c r="E70" s="1">
-        <f t="shared" si="3"/>
+      <c r="E120" s="1">
+        <f>IF(AND($B10&gt;0),(E10-$B10)/$B10,0)</f>
         <v>-0.46341463414634149</v>
       </c>
-      <c r="F70" s="1">
-        <f t="shared" si="3"/>
+      <c r="F120" s="1">
+        <f>IF(AND($B10&gt;0),(F10-$B10)/$B10,0)</f>
         <v>-0.66829268292682931</v>
       </c>
-      <c r="G70" s="1">
-        <f t="shared" si="3"/>
+      <c r="G120" s="1">
+        <f>IF(AND($B10&gt;0),(G10-$B10)/$B10,0)</f>
         <v>-0.69268292682926824</v>
       </c>
-      <c r="H70" s="1">
-        <f t="shared" si="3"/>
+      <c r="H120" s="1">
+        <f>IF(AND($B10&gt;0),(H10-$B10)/$B10,0)</f>
         <v>-0.79512195121951224</v>
       </c>
-      <c r="I70" s="2">
-        <f t="shared" si="3"/>
+      <c r="I120" s="2">
+        <f>IF(AND($B10&gt;0),(I10-$B10)/$B10,0)</f>
         <v>-0.82926829268292679</v>
       </c>
+      <c r="J120" s="16"/>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A71" s="12" t="str">
-        <f t="shared" ref="A71" si="10">A11</f>
-        <v xml:space="preserve"> 2^22 (4194304)    </v>
-      </c>
-      <c r="B71" s="1">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A121" s="11" t="str">
+        <f>A11</f>
+        <v xml:space="preserve">2^22 (4194304)    </v>
+      </c>
+      <c r="B121" s="1">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="C71" s="1">
-        <f t="shared" si="3"/>
+      <c r="C121" s="1">
+        <f>IF(AND($B11&gt;0),(C11-$B11)/$B11,0)</f>
         <v>-0.49184149184149184</v>
       </c>
-      <c r="D71" s="1">
-        <f t="shared" si="3"/>
+      <c r="D121" s="1">
+        <f>IF(AND($B11&gt;0),(D11-$B11)/$B11,0)</f>
         <v>-0.45687645687645689</v>
       </c>
-      <c r="E71" s="1">
-        <f t="shared" si="3"/>
+      <c r="E121" s="1">
+        <f>IF(AND($B11&gt;0),(E11-$B11)/$B11,0)</f>
         <v>-0.48717948717948717</v>
       </c>
-      <c r="F71" s="1">
-        <f t="shared" si="3"/>
+      <c r="F121" s="1">
+        <f>IF(AND($B11&gt;0),(F11-$B11)/$B11,0)</f>
         <v>-0.67832167832167833</v>
       </c>
-      <c r="G71" s="1">
-        <f t="shared" si="3"/>
+      <c r="G121" s="1">
+        <f>IF(AND($B11&gt;0),(G11-$B11)/$B11,0)</f>
         <v>-0.69696969696969702</v>
       </c>
-      <c r="H71" s="1">
-        <f t="shared" si="3"/>
+      <c r="H121" s="1">
+        <f>IF(AND($B11&gt;0),(H11-$B11)/$B11,0)</f>
         <v>-0.80885780885780889</v>
       </c>
-      <c r="I71" s="2">
-        <f t="shared" si="3"/>
+      <c r="I121" s="2">
+        <f>IF(AND($B11&gt;0),(I11-$B11)/$B11,0)</f>
         <v>-0.8601398601398601</v>
       </c>
+      <c r="J121" s="16"/>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A72" s="12" t="str">
-        <f t="shared" ref="A72" si="11">A12</f>
-        <v xml:space="preserve"> 2^23 (8388608)    </v>
-      </c>
-      <c r="B72" s="1">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A122" s="11" t="str">
+        <f>A12</f>
+        <v xml:space="preserve">2^23 (8388608)    </v>
+      </c>
+      <c r="B122" s="1">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="C72" s="1">
-        <f t="shared" si="3"/>
+      <c r="C122" s="1">
+        <f>IF(AND($B12&gt;0),(C12-$B12)/$B12,0)</f>
         <v>-0.46702127659574466</v>
       </c>
-      <c r="D72" s="1">
-        <f t="shared" si="3"/>
+      <c r="D122" s="1">
+        <f>IF(AND($B12&gt;0),(D12-$B12)/$B12,0)</f>
         <v>-0.48829787234042554</v>
       </c>
-      <c r="E72" s="1">
-        <f t="shared" si="3"/>
+      <c r="E122" s="1">
+        <f>IF(AND($B12&gt;0),(E12-$B12)/$B12,0)</f>
         <v>-0.46276595744680848</v>
       </c>
-      <c r="F72" s="1">
-        <f t="shared" si="3"/>
+      <c r="F122" s="1">
+        <f>IF(AND($B12&gt;0),(F12-$B12)/$B12,0)</f>
         <v>-0.71170212765957441</v>
       </c>
-      <c r="G72" s="1">
-        <f t="shared" si="3"/>
+      <c r="G122" s="1">
+        <f>IF(AND($B12&gt;0),(G12-$B12)/$B12,0)</f>
         <v>-0.7</v>
       </c>
-      <c r="H72" s="1">
-        <f t="shared" si="3"/>
+      <c r="H122" s="1">
+        <f>IF(AND($B12&gt;0),(H12-$B12)/$B12,0)</f>
         <v>-0.81382978723404253</v>
       </c>
-      <c r="I72" s="2">
-        <f t="shared" si="3"/>
+      <c r="I122" s="2">
+        <f>IF(AND($B12&gt;0),(I12-$B12)/$B12,0)</f>
         <v>-0.86276595744680851</v>
       </c>
+      <c r="J122" s="16"/>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A73" s="12" t="str">
-        <f t="shared" ref="A73" si="12">A13</f>
-        <v xml:space="preserve"> 2^24 (16777216)   </v>
-      </c>
-      <c r="B73" s="1">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A123" s="11" t="str">
+        <f>A13</f>
+        <v xml:space="preserve">2^24 (16777216)   </v>
+      </c>
+      <c r="B123" s="1">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="C73" s="1">
-        <f t="shared" si="3"/>
+      <c r="C123" s="1">
+        <f>IF(AND($B13&gt;0),(C13-$B13)/$B13,0)</f>
         <v>-0.48222565687789798</v>
       </c>
-      <c r="D73" s="1">
-        <f t="shared" si="3"/>
+      <c r="D123" s="1">
+        <f>IF(AND($B13&gt;0),(D13-$B13)/$B13,0)</f>
         <v>-0.49613601236476046</v>
       </c>
-      <c r="E73" s="1">
-        <f t="shared" si="3"/>
+      <c r="E123" s="1">
+        <f>IF(AND($B13&gt;0),(E13-$B13)/$B13,0)</f>
         <v>-0.48531684698608962</v>
       </c>
-      <c r="F73" s="1">
-        <f t="shared" si="3"/>
+      <c r="F123" s="1">
+        <f>IF(AND($B13&gt;0),(F13-$B13)/$B13,0)</f>
         <v>-0.71148892323544566</v>
       </c>
-      <c r="G73" s="1">
-        <f t="shared" si="3"/>
+      <c r="G123" s="1">
+        <f>IF(AND($B13&gt;0),(G13-$B13)/$B13,0)</f>
         <v>-0.71303451828954145</v>
       </c>
-      <c r="H73" s="1">
-        <f t="shared" si="3"/>
+      <c r="H123" s="1">
+        <f>IF(AND($B13&gt;0),(H13-$B13)/$B13,0)</f>
         <v>-0.81813498196805767</v>
       </c>
-      <c r="I73" s="2">
-        <f t="shared" si="3"/>
+      <c r="I123" s="2">
+        <f>IF(AND($B13&gt;0),(I13-$B13)/$B13,0)</f>
         <v>-0.86141164348274091</v>
       </c>
+      <c r="J123" s="16"/>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A74" s="13" t="str">
-        <f t="shared" ref="A74" si="13">A14</f>
-        <v xml:space="preserve"> 2^25 (33554432)   </v>
-      </c>
-      <c r="B74" s="3">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A124" s="12" t="str">
+        <f>A14</f>
+        <v xml:space="preserve">2^25 (33554432)   </v>
+      </c>
+      <c r="B124" s="3">
         <f>0</f>
         <v>0</v>
       </c>
-      <c r="C74" s="3">
-        <f t="shared" si="3"/>
+      <c r="C124" s="3">
+        <f>IF(AND($B14&gt;0),(C14-$B14)/$B14,0)</f>
         <v>-0.4729591836734694</v>
       </c>
-      <c r="D74" s="3">
-        <f t="shared" si="3"/>
+      <c r="D124" s="3">
+        <f>IF(AND($B14&gt;0),(D14-$B14)/$B14,0)</f>
         <v>-0.47525510204081634</v>
       </c>
-      <c r="E74" s="3">
-        <f t="shared" si="3"/>
+      <c r="E124" s="3">
+        <f>IF(AND($B14&gt;0),(E14-$B14)/$B14,0)</f>
         <v>-0.47423469387755102</v>
       </c>
-      <c r="F74" s="3">
-        <f t="shared" si="3"/>
+      <c r="F124" s="3">
+        <f>IF(AND($B14&gt;0),(F14-$B14)/$B14,0)</f>
         <v>-0.71071428571428574</v>
       </c>
-      <c r="G74" s="3">
-        <f t="shared" si="3"/>
+      <c r="G124" s="3">
+        <f>IF(AND($B14&gt;0),(G14-$B14)/$B14,0)</f>
         <v>-0.70204081632653059</v>
       </c>
-      <c r="H74" s="3">
-        <f t="shared" si="3"/>
+      <c r="H124" s="3">
+        <f>IF(AND($B14&gt;0),(H14-$B14)/$B14,0)</f>
         <v>-0.81632653061224492</v>
       </c>
-      <c r="I74" s="4">
-        <f t="shared" si="3"/>
+      <c r="I124" s="4">
+        <f>IF(AND($B14&gt;0),(I14-$B14)/$B14,0)</f>
         <v>-0.85765306122448981</v>
       </c>
+      <c r="J124" s="16"/>
+    </row>
+    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A125" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B125" s="3">
+        <v>0</v>
+      </c>
+      <c r="C125" s="18">
+        <f>-(2-1)</f>
+        <v>-1</v>
+      </c>
+      <c r="D125" s="18">
+        <f>-(3-1)</f>
+        <v>-2</v>
+      </c>
+      <c r="E125" s="18">
+        <f>-(4-1)</f>
+        <v>-3</v>
+      </c>
+      <c r="F125" s="18">
+        <f>-(6-1)</f>
+        <v>-5</v>
+      </c>
+      <c r="G125" s="18">
+        <f>-(8-1)</f>
+        <v>-7</v>
+      </c>
+      <c r="H125" s="18">
+        <f>-(16-1)</f>
+        <v>-15</v>
+      </c>
+      <c r="I125" s="19">
+        <f>-(32-1)</f>
+        <v>-31</v>
+      </c>
+      <c r="J125" s="15"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A61:I61"/>
+  <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
